--- a/data/0_raw/beef_stock_data.xlsx
+++ b/data/0_raw/beef_stock_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1070"/>
+  <dimension ref="A1:E1093"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22849,77 +22849,542 @@
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>등록 된 자료가 없습니다</t>
-        </is>
-      </c>
-      <c r="C1068" t="inlineStr">
-        <is>
-          <t>등록 된 자료가 없습니다</t>
-        </is>
-      </c>
-      <c r="D1068" t="inlineStr">
-        <is>
-          <t>등록 된 자료가 없습니다</t>
-        </is>
-      </c>
-      <c r="E1068" t="inlineStr">
-        <is>
-          <t>등록 된 자료가 없습니다</t>
-        </is>
+          <t>안심</t>
+        </is>
+      </c>
+      <c r="C1068" t="n">
+        <v>807</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>95</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>106</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>등록 된 자료가 없습니다</t>
-        </is>
-      </c>
-      <c r="C1069" t="inlineStr">
-        <is>
-          <t>등록 된 자료가 없습니다</t>
-        </is>
-      </c>
-      <c r="D1069" t="inlineStr">
-        <is>
-          <t>등록 된 자료가 없습니다</t>
-        </is>
-      </c>
-      <c r="E1069" t="inlineStr">
-        <is>
-          <t>등록 된 자료가 없습니다</t>
-        </is>
+          <t>등심</t>
+        </is>
+      </c>
+      <c r="C1069" t="n">
+        <v>6187</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>104</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>등록 된 자료가 없습니다</t>
-        </is>
-      </c>
-      <c r="C1070" t="inlineStr">
-        <is>
-          <t>등록 된 자료가 없습니다</t>
-        </is>
-      </c>
-      <c r="D1070" t="inlineStr">
-        <is>
-          <t>등록 된 자료가 없습니다</t>
-        </is>
-      </c>
-      <c r="E1070" t="inlineStr">
-        <is>
-          <t>등록 된 자료가 없습니다</t>
-        </is>
+          <t>채끝</t>
+        </is>
+      </c>
+      <c r="C1070" t="n">
+        <v>589</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>94</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>목심</t>
+        </is>
+      </c>
+      <c r="C1071" t="n">
+        <v>3651</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>88</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>앞다리</t>
+        </is>
+      </c>
+      <c r="C1072" t="n">
+        <v>7994</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>94</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>우둔</t>
+        </is>
+      </c>
+      <c r="C1073" t="n">
+        <v>3667</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>105</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>설도</t>
+        </is>
+      </c>
+      <c r="C1074" t="n">
+        <v>4283</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>107</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>양지</t>
+        </is>
+      </c>
+      <c r="C1075" t="n">
+        <v>18082</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>95</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>사태</t>
+        </is>
+      </c>
+      <c r="C1076" t="n">
+        <v>3451</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>109</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>갈비</t>
+        </is>
+      </c>
+      <c r="C1077" t="n">
+        <v>40296</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>99</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C1078" t="n">
+        <v>8068</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>86</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>부산물</t>
+        </is>
+      </c>
+      <c r="C1079" t="n">
+        <v>26446</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>94</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C1080" t="n">
+        <v>123521</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>96</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>안심</t>
+        </is>
+      </c>
+      <c r="C1081" t="n">
+        <v>834</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>103</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>등심</t>
+        </is>
+      </c>
+      <c r="C1082" t="n">
+        <v>7585</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>123</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>채끝</t>
+        </is>
+      </c>
+      <c r="C1083" t="n">
+        <v>586</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>목심</t>
+        </is>
+      </c>
+      <c r="C1084" t="n">
+        <v>4589</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>126</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>앞다리</t>
+        </is>
+      </c>
+      <c r="C1085" t="n">
+        <v>9338</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>117</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>우둔</t>
+        </is>
+      </c>
+      <c r="C1086" t="n">
+        <v>4556</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>124</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>설도</t>
+        </is>
+      </c>
+      <c r="C1087" t="n">
+        <v>4743</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>111</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>양지</t>
+        </is>
+      </c>
+      <c r="C1088" t="n">
+        <v>19863</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>110</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>사태</t>
+        </is>
+      </c>
+      <c r="C1089" t="n">
+        <v>3154</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>91</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>갈비</t>
+        </is>
+      </c>
+      <c r="C1090" t="n">
+        <v>43279</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>107</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C1091" t="n">
+        <v>8350</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>104</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>부산물</t>
+        </is>
+      </c>
+      <c r="C1092" t="n">
+        <v>26127</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>99</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C1093" t="n">
+        <v>133004</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>108</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/data/0_raw/beef_stock_data.xlsx
+++ b/data/0_raw/beef_stock_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1093"/>
+  <dimension ref="A1:E1106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23387,6 +23387,279 @@
         <v>92</v>
       </c>
     </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>안심</t>
+        </is>
+      </c>
+      <c r="C1094" t="n">
+        <v>803</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>96</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>등심</t>
+        </is>
+      </c>
+      <c r="C1095" t="n">
+        <v>7184</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>95</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>채끝</t>
+        </is>
+      </c>
+      <c r="C1096" t="n">
+        <v>588</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>목심</t>
+        </is>
+      </c>
+      <c r="C1097" t="n">
+        <v>3918</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>앞다리</t>
+        </is>
+      </c>
+      <c r="C1098" t="n">
+        <v>7700</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>83</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>우둔</t>
+        </is>
+      </c>
+      <c r="C1099" t="n">
+        <v>4389</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>96</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>설도</t>
+        </is>
+      </c>
+      <c r="C1100" t="n">
+        <v>4110</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>87</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>양지</t>
+        </is>
+      </c>
+      <c r="C1101" t="n">
+        <v>18860</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>95</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>사태</t>
+        </is>
+      </c>
+      <c r="C1102" t="n">
+        <v>2242</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>71</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>갈비</t>
+        </is>
+      </c>
+      <c r="C1103" t="n">
+        <v>38597</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>89</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C1104" t="n">
+        <v>8401</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>101</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>부산물</t>
+        </is>
+      </c>
+      <c r="C1105" t="n">
+        <v>23942</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>92</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C1106" t="n">
+        <v>120734</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>91</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/beef_stock_data.xlsx
+++ b/data/0_raw/beef_stock_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,31 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1106"/>
+  <dimension ref="A1:E1119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>기준년월</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>부위별 부위별</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>조사재고량 조사재고량</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>대비(%) 전월</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>대비(%) 전년</t>
         </is>
@@ -23658,6 +23646,279 @@
       </c>
       <c r="E1106" t="n">
         <v>92</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>안심</t>
+        </is>
+      </c>
+      <c r="C1107" t="n">
+        <v>828</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>103</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>등심</t>
+        </is>
+      </c>
+      <c r="C1108" t="n">
+        <v>6724</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>94</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>채끝</t>
+        </is>
+      </c>
+      <c r="C1109" t="n">
+        <v>695</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>118</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>목심</t>
+        </is>
+      </c>
+      <c r="C1110" t="n">
+        <v>3399</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>87</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>앞다리</t>
+        </is>
+      </c>
+      <c r="C1111" t="n">
+        <v>6997</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>91</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>우둔</t>
+        </is>
+      </c>
+      <c r="C1112" t="n">
+        <v>4076</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>93</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>설도</t>
+        </is>
+      </c>
+      <c r="C1113" t="n">
+        <v>3321</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>81</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>양지</t>
+        </is>
+      </c>
+      <c r="C1114" t="n">
+        <v>19194</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>102</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>사태</t>
+        </is>
+      </c>
+      <c r="C1115" t="n">
+        <v>2201</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>98</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>갈비</t>
+        </is>
+      </c>
+      <c r="C1116" t="n">
+        <v>37574</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>97</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C1117" t="n">
+        <v>8097</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>96</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>부산물</t>
+        </is>
+      </c>
+      <c r="C1118" t="n">
+        <v>23361</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>98</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C1119" t="n">
+        <v>116467</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>97</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/data/0_raw/beef_stock_data.xlsx
+++ b/data/0_raw/beef_stock_data.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,31 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1119"/>
+  <dimension ref="A1:E1131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>기준년월</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>부위별 부위별</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>조사재고량 조사재고량</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>대비(%) 전월</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>대비(%) 전년</t>
         </is>
@@ -23919,6 +23931,258 @@
       </c>
       <c r="E1119" t="n">
         <v>90</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>안심</t>
+        </is>
+      </c>
+      <c r="C1120" t="n">
+        <v>830</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>등심</t>
+        </is>
+      </c>
+      <c r="C1121" t="n">
+        <v>6601</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>98</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>채끝</t>
+        </is>
+      </c>
+      <c r="C1122" t="n">
+        <v>681</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>98</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>목심</t>
+        </is>
+      </c>
+      <c r="C1123" t="n">
+        <v>3426</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>101</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>앞다리</t>
+        </is>
+      </c>
+      <c r="C1124" t="n">
+        <v>7176</v>
+      </c>
+      <c r="D1124" t="n">
+        <v>103</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>우둔</t>
+        </is>
+      </c>
+      <c r="C1125" t="n">
+        <v>4253</v>
+      </c>
+      <c r="D1125" t="n">
+        <v>104</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>설도</t>
+        </is>
+      </c>
+      <c r="C1126" t="n">
+        <v>3151</v>
+      </c>
+      <c r="D1126" t="n">
+        <v>95</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>양지</t>
+        </is>
+      </c>
+      <c r="C1127" t="n">
+        <v>18037</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>94</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>사태</t>
+        </is>
+      </c>
+      <c r="C1128" t="n">
+        <v>1882</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>86</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>갈비</t>
+        </is>
+      </c>
+      <c r="C1129" t="n">
+        <v>37436</v>
+      </c>
+      <c r="D1129" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C1130" t="n">
+        <v>8256</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>102</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C1131" t="n">
+        <v>114478</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>98</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/0_raw/beef_stock_data.xlsx
+++ b/data/0_raw/beef_stock_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1131"/>
+  <dimension ref="A1:E1144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24185,6 +24185,279 @@
         <v>89</v>
       </c>
     </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>안심</t>
+        </is>
+      </c>
+      <c r="C1132" t="n">
+        <v>866</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>104</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>등심</t>
+        </is>
+      </c>
+      <c r="C1133" t="n">
+        <v>7195</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>109</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>채끝</t>
+        </is>
+      </c>
+      <c r="C1134" t="n">
+        <v>746</v>
+      </c>
+      <c r="D1134" t="n">
+        <v>110</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>목심</t>
+        </is>
+      </c>
+      <c r="C1135" t="n">
+        <v>3924</v>
+      </c>
+      <c r="D1135" t="n">
+        <v>115</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>앞다리</t>
+        </is>
+      </c>
+      <c r="C1136" t="n">
+        <v>7478</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>104</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>우둔</t>
+        </is>
+      </c>
+      <c r="C1137" t="n">
+        <v>4903</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>115</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>설도</t>
+        </is>
+      </c>
+      <c r="C1138" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>112</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>양지</t>
+        </is>
+      </c>
+      <c r="C1139" t="n">
+        <v>18188</v>
+      </c>
+      <c r="D1139" t="n">
+        <v>101</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>사태</t>
+        </is>
+      </c>
+      <c r="C1140" t="n">
+        <v>1746</v>
+      </c>
+      <c r="D1140" t="n">
+        <v>93</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>갈비</t>
+        </is>
+      </c>
+      <c r="C1141" t="n">
+        <v>38715</v>
+      </c>
+      <c r="D1141" t="n">
+        <v>103</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C1142" t="n">
+        <v>9410</v>
+      </c>
+      <c r="D1142" t="n">
+        <v>114</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>부산물</t>
+        </is>
+      </c>
+      <c r="C1143" t="n">
+        <v>22725</v>
+      </c>
+      <c r="D1143" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C1144" t="n">
+        <v>119413</v>
+      </c>
+      <c r="D1144" t="n">
+        <v>104</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
